--- a/Models/Молоко/results/Молоко - Результаты прогнозов SARIMA средние.xlsx
+++ b/Models/Молоко/results/Молоко - Результаты прогнозов SARIMA средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1825.95</v>
+        <v>1812.26</v>
       </c>
       <c r="C2" t="n">
-        <v>1705.76</v>
+        <v>1639.63</v>
       </c>
       <c r="D2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1225.38</v>
+        <v>1316.29</v>
       </c>
       <c r="C3" t="n">
-        <v>1164.08</v>
+        <v>1202.32</v>
       </c>
       <c r="D3" t="n">
-        <v>8.220000000000001</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4890.12</v>
+        <v>2293.38</v>
       </c>
       <c r="C4" t="n">
-        <v>4317.59</v>
+        <v>2066.48</v>
       </c>
       <c r="D4" t="n">
-        <v>16.55</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>219.63</v>
+        <v>215.62</v>
       </c>
       <c r="C5" t="n">
-        <v>199.04</v>
+        <v>194.89</v>
       </c>
       <c r="D5" t="n">
-        <v>10.06</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4213.97</v>
+        <v>2998.89</v>
       </c>
       <c r="C6" t="n">
-        <v>3709.49</v>
+        <v>2561.98</v>
       </c>
       <c r="D6" t="n">
-        <v>16.93</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.52</v>
+        <v>27.56</v>
       </c>
       <c r="C7" t="n">
-        <v>30.29</v>
+        <v>22.93</v>
       </c>
       <c r="D7" t="n">
-        <v>104.99</v>
+        <v>81.36</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="C8" t="n">
-        <v>1.93</v>
+        <v>2.49</v>
       </c>
       <c r="D8" t="n">
-        <v>12.35</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>537.04</v>
+        <v>590.55</v>
       </c>
       <c r="C9" t="n">
-        <v>498.23</v>
+        <v>544.9400000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>8.449999999999999</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>831.64</v>
+        <v>802.53</v>
       </c>
       <c r="C10" t="n">
-        <v>793.86</v>
+        <v>714.89</v>
       </c>
       <c r="D10" t="n">
-        <v>5.5</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1854.18</v>
+        <v>1978.45</v>
       </c>
       <c r="C11" t="n">
-        <v>1746.65</v>
+        <v>1811.75</v>
       </c>
       <c r="D11" t="n">
-        <v>9.18</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1351.07</v>
+        <v>929.3200000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>1146.76</v>
+        <v>754.61</v>
       </c>
       <c r="D12" t="n">
-        <v>6.69</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2088.81</v>
+        <v>1479.49</v>
       </c>
       <c r="C13" t="n">
-        <v>1924.3</v>
+        <v>1344.3</v>
       </c>
       <c r="D13" t="n">
-        <v>11.37</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>799.58</v>
+        <v>2168.01</v>
       </c>
       <c r="C14" t="n">
-        <v>568.22</v>
+        <v>1376.51</v>
       </c>
       <c r="D14" t="n">
-        <v>13.48</v>
+        <v>27.65</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1.79979758155598e+17</v>
+        <v>206.67</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4446.31</v>
+        <v>584.39</v>
       </c>
       <c r="C16" t="n">
-        <v>3958.25</v>
+        <v>441.84</v>
       </c>
       <c r="D16" t="n">
-        <v>17.57</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2205.07</v>
+        <v>374.43</v>
       </c>
       <c r="C17" t="n">
-        <v>2009.53</v>
+        <v>326.52</v>
       </c>
       <c r="D17" t="n">
-        <v>12.86</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1937.84</v>
+        <v>1038.68</v>
       </c>
       <c r="C18" t="n">
-        <v>1588.06</v>
+        <v>867.17</v>
       </c>
       <c r="D18" t="n">
-        <v>46.78</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2829.19</v>
+        <v>3383.01</v>
       </c>
       <c r="C19" t="n">
-        <v>2600.22</v>
+        <v>3076</v>
       </c>
       <c r="D19" t="n">
-        <v>13.64</v>
+        <v>16.39</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6603.67</v>
+        <v>3935.92</v>
       </c>
       <c r="C20" t="n">
-        <v>5780.13</v>
+        <v>3545.51</v>
       </c>
       <c r="D20" t="n">
-        <v>19.24</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3297.07</v>
+        <v>5139.17</v>
       </c>
       <c r="C21" t="n">
-        <v>3044.5</v>
+        <v>4539.2</v>
       </c>
       <c r="D21" t="n">
-        <v>8.81</v>
+        <v>11.39</v>
       </c>
     </row>
   </sheetData>
